--- a/Java24 QuyenPhan Database Design.xlsx
+++ b/Java24 QuyenPhan Database Design.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qphan\Desktop\bkit\course - webapp\java24\3. Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A1CA67-5D9C-4923-BD38-6E31515EA46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D252159-A958-446A-81C4-1957C4239430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="363" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B1. Mô hình quan niệm" sheetId="1" r:id="rId1"/>
+    <sheet name="B2. Mô hình logic" sheetId="2" r:id="rId2"/>
+    <sheet name="B3. Cơ sở dữ liệu vật lý" sheetId="3" r:id="rId3"/>
+    <sheet name="B4. Database" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,8 +27,1248 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={C782911D-FE2E-49D3-A60F-87DB53FBA471}</author>
+  </authors>
+  <commentList>
+    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{C782911D-FE2E-49D3-A60F-87DB53FBA471}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Số lượng còn loại</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Quyen Ngoc Phan</author>
+  </authors>
+  <commentList>
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{9BE57048-D524-45DE-AE5F-50871BB4BF6C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+S M L XL XXL</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P6" authorId="0" shapeId="0" xr:uid="{4A5762AC-09FF-41FD-85EC-37275D8C17E6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+VAT
+DAT
+BAC</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{DE667DB8-DA17-40C1-80DA-7CCBA4777769}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>nullable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{66A4F5EF-04F9-45F0-8FFA-0FF14A0CDC59}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0/1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{84CD022B-443C-4221-9AE1-3EBF1557A927}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Unique</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{3B9DE024-0B36-4A0E-91BB-3FF023E4AF1C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Unique</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{55601015-5266-46DD-814E-97C36FA3D67D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+nullable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{086AF797-241C-4CAA-BD0F-6581BCFB3386}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mặt hàng khác kích thước có thể khác giá bán
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{D0C221EB-3198-44EA-A32A-724381B88FD6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mặt hàng có thể có giá mua khác nhau cho mỗi lô hàng
+Có thể lưu trữ giá mới nhất ở đây hoặc không</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{AA26C434-80FC-4D3A-9C1B-DEDC5E839931}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Lúc tính tổng tiền
+Nhớ kèm thuế</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{E954F478-0E9D-4709-B23E-D041C5C19823}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mã Hóa</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{77E3D814-068C-4F10-9818-D3502F9FF281}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mã Hóa</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{565BA2E9-86AF-4FB2-A055-1A5919640B31}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0/1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q12" authorId="0" shapeId="0" xr:uid="{89F9ACA7-57F0-4B93-9659-7C67FBA5DAF6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+null: tồn tại trong giỏ hàng
+not-null: trở thành đơn hàng, ko load ra UI chỗ giỏ hàng</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q13" authorId="0" shapeId="0" xr:uid="{CA7A3A8D-9704-4E4F-BADC-F2D28040DA68}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1 Khách Hàng - 1 Giỏ Hàng - N Mặt Hàng - Đưa Mặt Hàng xuống dưới
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{C64AA1A1-6544-4A9A-ACB8-51D5AE2083BE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Số lượng mặt hàng còn lại trong hệ thống, kho</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Quyen Ngoc Phan</author>
+  </authors>
+  <commentList>
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{82D4A7D0-C6E4-4EB1-89C7-4FF9634032FD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+S M L XL XXL</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P6" authorId="0" shapeId="0" xr:uid="{17F14DB5-A770-45E1-8ADC-0D1CB5D07B19}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+VAT
+DAT
+BAC</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{6E4BCAA1-E0CA-40E2-A180-17B5938D98FC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>nullable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{99236802-8271-41CE-BC2F-CA7DB178C880}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0/1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{33D98EBD-ADF8-4C3F-851E-416053C87ADC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Unique</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{E6733628-96D6-459F-80F9-6F68D2DCA644}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Unique</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{AFEF85DF-04A4-4744-AF7E-A52A3620BA60}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+nullable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{2A8E8AE7-B41C-4D27-B5F4-C9112BE379DC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mặt hàng khác kích thước có thể khác giá bán
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{A57CAB91-1A2A-42CC-98B5-1FFF5E2025A2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mặt hàng có thể có giá mua khác nhau cho mỗi lô hàng
+Có thể lưu trữ giá mới nhất ở đây hoặc không</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{73BB5E20-9B25-4164-8B1F-C1B233BE1F52}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Lúc tính tổng tiền
+Nhớ kèm thuế</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{815C0325-FA60-4DA6-A239-7E5ED74294B0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mã Hóa</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{A7FE6F74-D8DE-41E0-BE69-CB227E17D10C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mã Hóa</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{B1EFDAA5-BFFA-4596-B39F-F7D6431C89EE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0/1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q12" authorId="0" shapeId="0" xr:uid="{4ACCF10E-AF54-4932-A572-A7AAAD21F2B4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+null: tồn tại trong giỏ hàng
+not-null: trở thành đơn hàng, ko load ra UI chỗ giỏ hàng</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q13" authorId="0" shapeId="0" xr:uid="{93F8BCC7-671B-49B8-849C-4D8B21C523E0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1 Khách Hàng - 1 Giỏ Hàng - N Mặt Hàng - Đưa Mặt Hàng xuống dưới
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{F67183A5-F60D-4AC2-AB9D-84B85CF38709}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Số lượng mặt hàng còn lại trong hệ thống, kho</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D55" authorId="0" shapeId="0" xr:uid="{551E5488-73BE-4A8E-A66E-DDA6A73EECB5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0/1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D74" authorId="0" shapeId="0" xr:uid="{068C3CE0-FC7F-4871-A826-DB5A840DBF51}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Lúc tính tổng tiền
+Nhớ kèm thuế</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Quyen Ngoc Phan</author>
+  </authors>
+  <commentList>
+    <comment ref="W6" authorId="0" shapeId="0" xr:uid="{DB457082-B5BC-4CCE-AAD6-89F72A150709}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+VAT
+DAT
+BAC</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T7" authorId="0" shapeId="0" xr:uid="{6034391E-32E8-4DFA-8180-FC640051CA39}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>nullable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{CE1DD46D-95B7-4AF9-BF2E-D7377196D7CD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Số lượng nhập vào tại thời điểm nào đó</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{DC236AB2-2C11-4F09-9648-C970222ABF27}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0/1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P8" authorId="0" shapeId="0" xr:uid="{1CD97AC3-384E-4867-9604-5625700D109D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Unique</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q8" authorId="0" shapeId="0" xr:uid="{7739D246-54A3-47E1-9699-9BF663E788B3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Unique</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T8" authorId="0" shapeId="0" xr:uid="{2613782C-6E79-4403-9805-5FF255D2EF6E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+nullable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{339E44D0-A5F1-4C01-98F8-AC8FC49CF893}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mặt hàng khác màu sắc thì là mặt hàng khác
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K10" authorId="0" shapeId="0" xr:uid="{18BB5900-BA99-40D2-8520-1D4ACDFD2899}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Lúc tính tổng tiền
+Nhớ kèm thuế</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P11" authorId="0" shapeId="0" xr:uid="{96297396-FEC8-4A81-8A6B-A7129677071D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mã Hóa</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q11" authorId="0" shapeId="0" xr:uid="{0B318388-DA7F-4127-99DD-E460BF12018F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Mã Hóa</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T11" authorId="0" shapeId="0" xr:uid="{D4891D8A-A215-4AD3-9C5C-07B875A9C1EB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0/1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X12" authorId="0" shapeId="0" xr:uid="{C9488E0B-9209-4832-B800-8EEC65EA25A7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+null: tồn tại trong giỏ hàng
+not-null: trở thành đơn hàng, ko load ra UI chỗ giỏ hàng</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X13" authorId="0" shapeId="0" xr:uid="{94FAE571-4485-4751-A624-78DB7B3E3B39}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+1 Khách Hàng - 1 Giỏ Hàng - N Mặt Hàng - Đưa Mặt Hàng xuống dưới
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H56" authorId="0" shapeId="0" xr:uid="{8F332342-97CA-40D7-90EF-C0D4C39BA1FC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+0/1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H75" authorId="0" shapeId="0" xr:uid="{94511645-BFD9-4196-A589-4CE79279B2A4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Lúc tính tổng tiền
+Nhớ kèm thuế</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="314">
   <si>
     <t>MatHang</t>
   </si>
@@ -55,13 +1298,1251 @@
   </si>
   <si>
     <t>HinhAnh(s)</t>
+  </si>
+  <si>
+    <t>DonHang</t>
+  </si>
+  <si>
+    <t>MaDH</t>
+  </si>
+  <si>
+    <t>NgayDatHang</t>
+  </si>
+  <si>
+    <t>DiaChiNhanHang</t>
+  </si>
+  <si>
+    <t>SoDienThoaiNguoiNhan</t>
+  </si>
+  <si>
+    <t>HinhThucThanhToan</t>
+  </si>
+  <si>
+    <t>TongSoLuongCacMatHang</t>
+  </si>
+  <si>
+    <t>TongTien</t>
+  </si>
+  <si>
+    <t>PhiVanChuyen</t>
+  </si>
+  <si>
+    <t>MaKH</t>
+  </si>
+  <si>
+    <t>KhachHang</t>
+  </si>
+  <si>
+    <t>HoTen</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>DiaChi</t>
+  </si>
+  <si>
+    <t>SoDienThoai</t>
+  </si>
+  <si>
+    <t>MatKhau</t>
+  </si>
+  <si>
+    <t>DangNhapMangXaHoi</t>
+  </si>
+  <si>
+    <t>LoaiHang</t>
+  </si>
+  <si>
+    <t>MaLH</t>
+  </si>
+  <si>
+    <t>TenLH</t>
+  </si>
+  <si>
+    <t>TrangThaiLoaiHang</t>
+  </si>
+  <si>
+    <t>NhanVien</t>
+  </si>
+  <si>
+    <t>MaNV</t>
+  </si>
+  <si>
+    <t>TaiKhoanMangXaHoi</t>
+  </si>
+  <si>
+    <t>ChucVu</t>
+  </si>
+  <si>
+    <t>PhongBan</t>
+  </si>
+  <si>
+    <t>OOP: HAS-A IS-A</t>
+  </si>
+  <si>
+    <t>Database: HAS-A</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Xác định các </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đối tượng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của dự án</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Xác định các </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thông tin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cần lưu trữ của từng đối tượng</t>
+    </r>
+  </si>
+  <si>
+    <t>ChiTietDonHang</t>
+  </si>
+  <si>
+    <t>MaCTDH</t>
+  </si>
+  <si>
+    <t>PhieuNhapHang</t>
+  </si>
+  <si>
+    <t>NgayNhap</t>
+  </si>
+  <si>
+    <t>SoLuongNhap</t>
+  </si>
+  <si>
+    <t>GiaNhap</t>
+  </si>
+  <si>
+    <t>Áo sơ mi</t>
+  </si>
+  <si>
+    <t>SoLuongHangDaNhap</t>
+  </si>
+  <si>
+    <t>SoLuongHangConLai</t>
+  </si>
+  <si>
+    <t>SoLuongHangDaBan</t>
+  </si>
+  <si>
+    <t>SoLuong</t>
+  </si>
+  <si>
+    <t>DH01</t>
+  </si>
+  <si>
+    <t>DH02</t>
+  </si>
+  <si>
+    <t>DH03</t>
+  </si>
+  <si>
+    <t>Tiền mặt</t>
+  </si>
+  <si>
+    <t>SoLuongMatHang</t>
+  </si>
+  <si>
+    <t>Áo jean</t>
+  </si>
+  <si>
+    <t>Chức năng thống kê</t>
+  </si>
+  <si>
+    <t>Thực hiện truy vấn dữ liệu theo yêu cầu thông kê của người dùng</t>
+  </si>
+  <si>
+    <t>Không lưu trữ thông tin để/đã thống kê</t>
+  </si>
+  <si>
+    <t>SoLuongDatHang</t>
+  </si>
+  <si>
+    <t>MaDC</t>
+  </si>
+  <si>
+    <t>TenNguoiNhan</t>
+  </si>
+  <si>
+    <t>TrangThai</t>
+  </si>
+  <si>
+    <t>PhieuKhuyenMai</t>
+  </si>
+  <si>
+    <t>SoTienGiam</t>
+  </si>
+  <si>
+    <t>%Giam</t>
+  </si>
+  <si>
+    <t>NgayBatDau</t>
+  </si>
+  <si>
+    <t>NgayKetThuc</t>
+  </si>
+  <si>
+    <t>PhanQuyen</t>
+  </si>
+  <si>
+    <t>MaPQ</t>
+  </si>
+  <si>
+    <t>TenChucNang</t>
+  </si>
+  <si>
+    <t>ChiTietPhanQuyen</t>
+  </si>
+  <si>
+    <t>MaCTPQ</t>
+  </si>
+  <si>
+    <t>DC1</t>
+  </si>
+  <si>
+    <t>KH01</t>
+  </si>
+  <si>
+    <t>Le A</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>Hòa Khánh</t>
+  </si>
+  <si>
+    <t>DC2</t>
+  </si>
+  <si>
+    <t>Le Nam</t>
+  </si>
+  <si>
+    <t>Hải Châu</t>
+  </si>
+  <si>
+    <t>DiaChiGiaoHang</t>
+  </si>
+  <si>
+    <t>MaPhieu</t>
+  </si>
+  <si>
+    <t>*****</t>
+  </si>
+  <si>
+    <t>Thue</t>
+  </si>
+  <si>
+    <t>MaSoThue</t>
+  </si>
+  <si>
+    <t>LoaiThue</t>
+  </si>
+  <si>
+    <t>%Thue</t>
+  </si>
+  <si>
+    <t>TongThue</t>
+  </si>
+  <si>
+    <t>NgayNopThue</t>
+  </si>
+  <si>
+    <t>NguoiKhaiThue</t>
+  </si>
+  <si>
+    <t>Thuế mua hàng</t>
+  </si>
+  <si>
+    <t>Thuế bán hàng</t>
+  </si>
+  <si>
+    <t>Thuế trả tiền nhân viên</t>
+  </si>
+  <si>
+    <t>%ThueChoDonHang</t>
+  </si>
+  <si>
+    <t>TinhTrangDonHang</t>
+  </si>
+  <si>
+    <t>GioHang</t>
+  </si>
+  <si>
+    <t>NgayThemVaoGioHang</t>
+  </si>
+  <si>
+    <t>NgayXoaKhoiGioHang</t>
+  </si>
+  <si>
+    <t>DeMuaSau</t>
+  </si>
+  <si>
+    <t>MHA1</t>
+  </si>
+  <si>
+    <t>MHA2</t>
+  </si>
+  <si>
+    <t>Mô hình quan niệm</t>
+  </si>
+  <si>
+    <t>Mô hình logic(trên cơ sở đối tượng, mẫu tin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ** Dữ liệu không trùng nhau, vô nghĩa, tốn vùng nhớ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ** Hỗ trợ truy vấn với khóa nhanh hơn các thuộc tính thông thường</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ** Thông qua các cặp số min max, lưu ý chọn max ở mỗi bên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ** Có ba loại: 11 - 1n n1 - nn</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Xác định các </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tập thực thể</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Xác định các </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thuộc tính</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của mỗi tập thực thể(đơn trị, đa trị, kết hợp, dẫn xuất,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kiểu dữ liệu nguyên tố</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[không thể là một đối tượng, danh sách, chia nhỏ được nữa])</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. Xác định </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mối kết hợp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> giữa các tập thực thể</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">  $$ Thông tin - Thuộc tính - Cột</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  $$ Đối tượng - Tập thực thể - Bảng</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ** Khóa - Khóa chính</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ** Mỗi kết hợp - Khóa ngoại || Tạo các bảng mới</t>
+  </si>
+  <si>
+    <t>MH1</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>LHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ** https://drive.google.com/file/d/11x9RTdNb1Hw8ptkzpbUCe3BBjY8lBEYk/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Thẻ ghi nợ</t>
+  </si>
+  <si>
+    <t>Chuyển khoản</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Banking</t>
+  </si>
+  <si>
+    <t>MaHTTT</t>
+  </si>
+  <si>
+    <t>MoTa</t>
+  </si>
+  <si>
+    <t>HT1</t>
+  </si>
+  <si>
+    <t>HT2</t>
+  </si>
+  <si>
+    <t>HT3</t>
+  </si>
+  <si>
+    <t>SDTNguoiNhan</t>
+  </si>
+  <si>
+    <t>MatHang(s)</t>
+  </si>
+  <si>
+    <t>HoaDon</t>
+  </si>
+  <si>
+    <t>MaHD</t>
+  </si>
+  <si>
+    <t>PhiGiaoHang</t>
+  </si>
+  <si>
+    <t>TinhTrangDonHang(s)</t>
+  </si>
+  <si>
+    <t>GoogleMailToken</t>
+  </si>
+  <si>
+    <t>MaPB</t>
+  </si>
+  <si>
+    <t>TenPB</t>
+  </si>
+  <si>
+    <t>Tập thực thể kết hợp</t>
+  </si>
+  <si>
+    <t>của DH và MH - Chương 3</t>
+  </si>
+  <si>
+    <t>Không liên quan đến logic nhiều</t>
+  </si>
+  <si>
+    <t>Xử lý trong phần backend</t>
+  </si>
+  <si>
+    <t>TongTienPhaiNop</t>
+  </si>
+  <si>
+    <t>TuNgay</t>
+  </si>
+  <si>
+    <t>DenNgay</t>
+  </si>
+  <si>
+    <t>của KH và MH - Chương 3</t>
+  </si>
+  <si>
+    <t>KichThuoc</t>
+  </si>
+  <si>
+    <t>MaKichThuoc</t>
+  </si>
+  <si>
+    <t>GioiTinh</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Xác định </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>khóa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của tập thực thể(là tập ít nhất các thuộc tính dùng để phân biệt 2 thực thể với nhau, đảm bảo 2 thực thể khác nhau trong một tập thực thể dữ liệu của khóa không được trùng nhau</t>
+    </r>
+  </si>
+  <si>
+    <t>Clob, Blob</t>
+  </si>
+  <si>
+    <t>MauSac</t>
+  </si>
+  <si>
+    <t>MaGioHang</t>
+  </si>
+  <si>
+    <t>Mô hình cơ sở dữ liệu vật liệu</t>
+  </si>
+  <si>
+    <t>1. Tập thực thể</t>
+  </si>
+  <si>
+    <t>==</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>2. Thuộc tính</t>
+  </si>
+  <si>
+    <t>4. Mối kết hợp 11 1nn1 nn</t>
+  </si>
+  <si>
+    <t>Quan hệ 1-N với ví dụ là MatHang và LoaiHang</t>
+  </si>
+  <si>
+    <t>MH A1</t>
+  </si>
+  <si>
+    <t>MH A2</t>
+  </si>
+  <si>
+    <t>MH A3</t>
+  </si>
+  <si>
+    <t>Áo</t>
+  </si>
+  <si>
+    <t>Quần</t>
+  </si>
+  <si>
+    <t>Giày dép</t>
+  </si>
+  <si>
+    <t>Xanh</t>
+  </si>
+  <si>
+    <t>Đỏ</t>
+  </si>
+  <si>
+    <t>Đen</t>
+  </si>
+  <si>
+    <t>LH1</t>
+  </si>
+  <si>
+    <t>LH2</t>
+  </si>
+  <si>
+    <t>LH3</t>
+  </si>
+  <si>
+    <t>LH4</t>
+  </si>
+  <si>
+    <t>Loại Hàng 1</t>
+  </si>
+  <si>
+    <t>Loại Hàng 2</t>
+  </si>
+  <si>
+    <t>Loại Hàng 3</t>
+  </si>
+  <si>
+    <t>Loại Hàng 4</t>
+  </si>
+  <si>
+    <t>Thông thường: bảng 1 gọi là bảng cha và bảng N gọi là bảng con</t>
+  </si>
+  <si>
+    <t>FK</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Primary Key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Chọn ra khóa để cài đặt làm khóa chính(dữ liệu không trùng nhau)</t>
+    </r>
+  </si>
+  <si>
+    <t>Foreign Key - Tạo mối kết hợp, ràng buộc giữa các Table(tùy trường hợp)</t>
+  </si>
+  <si>
+    <t>- Nếu bảng 1 có khóa chính là 1 column, bên bảng N tạo 1 column khóa ngoại liên kết</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Nếu bảng 1 có khóa chính nhiều hơn 1 column, bên bảng N [tạo N columns làm khóa ngoại], </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>xử lý tốt hơn vào thực tế</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lý thuyết: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quan hệ 1 N thì bỏ 1 vào N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nghĩa là t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ạo một column mới làm khóa ngoại bên bảng N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> rồi tạo liên kết đến khóa chính bên bảng 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ví dụ 2: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SinhVien</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và LopSinhHoat</t>
+    </r>
+  </si>
+  <si>
+    <t>Mặc định: Column khóa ngoại, dữ liệu có thể trùng nhau</t>
+  </si>
+  <si>
+    <t>Quan hệ 1-1 với ví dụ là DonHang và HoaDon</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lý thuyết: Tạo </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>column mới làm khóa ngoại bên bất kỳ table nào</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lưu ý phải thêm ràng buộc UNIQUE cho column đó</t>
+    </r>
+  </si>
+  <si>
+    <t>DH1</t>
+  </si>
+  <si>
+    <t>DH2</t>
+  </si>
+  <si>
+    <t>DH3</t>
+  </si>
+  <si>
+    <t>22.10</t>
+  </si>
+  <si>
+    <t>[Cash]</t>
+  </si>
+  <si>
+    <t>[Debit]</t>
+  </si>
+  <si>
+    <t>[Credit]</t>
+  </si>
+  <si>
+    <t>HD X1</t>
+  </si>
+  <si>
+    <t>HD X2</t>
+  </si>
+  <si>
+    <t>FK + Unique</t>
+  </si>
+  <si>
+    <t>Quan hệ N-N với ví dụ là DonHang và MatHang</t>
+  </si>
+  <si>
+    <t>Lý thuyết: Tạo ra 1 table mới, table đó gọi là table quan hệ được tạo ra từ mối kết hợp N N</t>
+  </si>
+  <si>
+    <t>- Table mới có thể tạo thêm các column khác</t>
+  </si>
+  <si>
+    <t>- Table mới có ít nhất là 2 columns là khóa ngoại liên kết với khóa chính của 2 tables quan hệ, đồng thời 2 columns đó sẽ là khóa chính của table mới để đảm bảo dữ liệu chính xác</t>
+  </si>
+  <si>
+    <t>PK(MaHD, MaMH)</t>
+  </si>
+  <si>
+    <t>Column(nguyên tố)</t>
+  </si>
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>3. Khóa(chọn)</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>PK, FK</t>
+  </si>
+  <si>
+    <t>Cách làm khác với quan hệ 1-N</t>
+  </si>
+  <si>
+    <t>Trường hợp bảng N có quá nhiều column, thêm FK vào bị rối và dữ liệu nhiều truy vấn FK column tốn tài nguyên</t>
+  </si>
+  <si>
+    <t>ThongTinThanhToan</t>
+  </si>
+  <si>
+    <t>Cách làm khác với quan hệ 1-1</t>
+  </si>
+  <si>
+    <t>T01_ITEM</t>
+  </si>
+  <si>
+    <t>C01_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C01_ITEM_NAME</t>
+  </si>
+  <si>
+    <t>T02_SIZE</t>
+  </si>
+  <si>
+    <t>C02_SIZE_ID</t>
+  </si>
+  <si>
+    <t>C02_GENDER</t>
+  </si>
+  <si>
+    <t>C02_SIZE_DESC</t>
+  </si>
+  <si>
+    <t>T03_ITEM_DETAIL</t>
+  </si>
+  <si>
+    <t>C02_SIZE_NAME</t>
+  </si>
+  <si>
+    <t>Size S - Nu - Từ 40 đến 50kg</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>XXL</t>
+  </si>
+  <si>
+    <t>Size S - Nam - Từ 45 đến 55kg</t>
+  </si>
+  <si>
+    <t>Item A1</t>
+  </si>
+  <si>
+    <t>Item A2</t>
+  </si>
+  <si>
+    <t>UNIQUE</t>
+  </si>
+  <si>
+    <t>Item A3</t>
+  </si>
+  <si>
+    <t>Khi một table có khóa chính nhiều hơn 1 column</t>
+  </si>
+  <si>
+    <t>Xử lý</t>
+  </si>
+  <si>
+    <r>
+      <t>Và table(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>referenced table pk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) đó cần được tham chiếu từ table(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>referencing table fk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) khác, bảng tham chiếu sẽ cần phải có nhiều hơn 1 column làm khóa ngoại</t>
+    </r>
+  </si>
+  <si>
+    <t>Tạo column mới làm khóa chính đại diện cho table(referenced table)</t>
+  </si>
+  <si>
+    <t>Thêm ràng buộc UNIQUE cho các column pk cũ</t>
+  </si>
+  <si>
+    <t>Unique</t>
+  </si>
+  <si>
+    <t>C03_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C03_SIZE_ID</t>
+  </si>
+  <si>
+    <t>C03_SALES_PRICE</t>
+  </si>
+  <si>
+    <t>T04_WAREHOUSE_RECEIPT</t>
+  </si>
+  <si>
+    <t>C04_WHRECEIPT_ID</t>
+  </si>
+  <si>
+    <t>C04_WHRECEIPT_TIME</t>
+  </si>
+  <si>
+    <t>C04_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phiếu nhập kho | hàng </t>
+  </si>
+  <si>
+    <t>Tương tự đơn hàng</t>
+  </si>
+  <si>
+    <t>Kết hợp T01 T04</t>
+  </si>
+  <si>
+    <t>T05_WAREHOUSE_RECEIPT_DETAIL</t>
+  </si>
+  <si>
+    <t>C05_WHRECEIPT_ID</t>
+  </si>
+  <si>
+    <t>C05_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C05_AMOUNT</t>
+  </si>
+  <si>
+    <t>C05_BUY_PRICE</t>
+  </si>
+  <si>
+    <t>C05_PROVIDER_ID</t>
+  </si>
+  <si>
+    <t>T06_PROVIDER</t>
+  </si>
+  <si>
+    <t>C06_PROVIDER_ID</t>
+  </si>
+  <si>
+    <t>C06_PROVIDER_NAME</t>
+  </si>
+  <si>
+    <t>C06_PROVIDER_TAX</t>
+  </si>
+  <si>
+    <t>PK &amp; FK</t>
+  </si>
+  <si>
+    <t>C01_ITEM_GROUP_ID</t>
+  </si>
+  <si>
+    <t>T07_ITEM_GROUP</t>
+  </si>
+  <si>
+    <t>C07_ITEM_GROUP_ID</t>
+  </si>
+  <si>
+    <t>C07_ITEM_GROUP_NAME</t>
+  </si>
+  <si>
+    <t>C07_STATUS</t>
+  </si>
+  <si>
+    <t>C01_COLOR</t>
+  </si>
+  <si>
+    <t>Xử lý quan hệ 1-N với N không tồn tại table</t>
+  </si>
+  <si>
+    <t>T08_GALLERY</t>
+  </si>
+  <si>
+    <t>C08_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C08_IMAGE_PATH</t>
+  </si>
+  <si>
+    <t>file://img01.png</t>
+  </si>
+  <si>
+    <t>file://img02.png</t>
+  </si>
+  <si>
+    <t>file://img03.png</t>
+  </si>
+  <si>
+    <t>file://img04.png</t>
+  </si>
+  <si>
+    <t>file://img05.png</t>
+  </si>
+  <si>
+    <t>C03_AMOUNT</t>
+  </si>
+  <si>
+    <t>T09_ORDER</t>
+  </si>
+  <si>
+    <t>C09_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C09_ORDER_TIME</t>
+  </si>
+  <si>
+    <t>T11_PAYMENT_METHOD</t>
+  </si>
+  <si>
+    <t>C11_PAYMENT_METHOD_ID</t>
+  </si>
+  <si>
+    <t>C11_PAYMENT_METHOD_NAME</t>
+  </si>
+  <si>
+    <t>C09_PAYMENT_METHOD_ID</t>
+  </si>
+  <si>
+    <t>T12_ORDER_DETAIL</t>
+  </si>
+  <si>
+    <t>C12_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C12_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C12_AMOUNT</t>
+  </si>
+  <si>
+    <t>Enum</t>
+  </si>
+  <si>
+    <t>T13_ORDER_STATUS</t>
+  </si>
+  <si>
+    <t>C13_ORDER_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C13_ORDER_STATUS_DESC</t>
+  </si>
+  <si>
+    <t>T14_ORDER_STATUS_DETAIL</t>
+  </si>
+  <si>
+    <t>Kết hợp T01 T09</t>
+  </si>
+  <si>
+    <t>Kết hợp T09 và T13</t>
+  </si>
+  <si>
+    <t>C14_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C14_ORDER_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C14_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C14_LAST_UPDATED</t>
+  </si>
+  <si>
+    <t>C09_CUSTOMER_ID</t>
+  </si>
+  <si>
+    <t>C09_DELIVERY_ADDRESS_ID</t>
+  </si>
+  <si>
+    <t>C09_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>T10_BILL</t>
+  </si>
+  <si>
+    <t>C10_BILL_ID</t>
+  </si>
+  <si>
+    <t>C10_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C10_DELIVERY_FEE</t>
+  </si>
+  <si>
+    <t>C10_VOUCHER_ID</t>
+  </si>
+  <si>
+    <t>C10_TOTAL_OF_MONEY</t>
+  </si>
+  <si>
+    <t>T15_CUSTOMER</t>
+  </si>
+  <si>
+    <t>C15_CUSTOMER_ID</t>
+  </si>
+  <si>
+    <t>C15_CUSTOMER_NAME</t>
+  </si>
+  <si>
+    <t>C15_CUSTOMER_EMAIL</t>
+  </si>
+  <si>
+    <t>C15_CUSTOMER_ADDRESS</t>
+  </si>
+  <si>
+    <t>C15_CUSTOMER_PHONE</t>
+  </si>
+  <si>
+    <t>C15_CUSTOMER_PASSWORD</t>
+  </si>
+  <si>
+    <t>C15_GMAIL_TOKEN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,8 +2564,129 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -97,8 +2699,56 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -121,11 +2771,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -136,8 +2807,171 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -151,6 +2985,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Quyen Ngoc Phan" id="{AF552595-C243-4DB1-82EA-E8F193E73D49}" userId="S::Quyen.Ngoc.Phan@mgm-tp.com::a07336a7-4c4c-48f3-ae7a-f1af5b9df94c" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -414,152 +3254,312 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B15" dT="2025-06-22T07:40:29.93" personId="{AF552595-C243-4DB1-82EA-E8F193E73D49}" id="{C782911D-FE2E-49D3-A60F-87DB53FBA471}">
+    <text>Số lượng còn loại</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:M50"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="39" width="22.7109375" style="1" customWidth="1"/>
+    <col min="1" max="2" width="22.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" style="1" customWidth="1"/>
+    <col min="4" max="39" width="22.7109375" style="1" customWidth="1"/>
     <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
     <row r="5" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="6" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="7" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="C8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="9" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="10" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="11" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="C11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="I11" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="M12" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="13" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -575,7 +3575,9 @@
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -588,8 +3590,12 @@
       <c r="M14" s="2"/>
     </row>
     <row r="15" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -603,7 +3609,9 @@
     </row>
     <row r="16" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -617,7 +3625,9 @@
     </row>
     <row r="17" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -631,7 +3641,9 @@
     </row>
     <row r="18" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -658,37 +3670,4955 @@
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" s="1">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="I23" s="1">
+        <v>10.06</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+      <c r="G24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="1">
+        <v>260</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="1">
+        <v>21</v>
+      </c>
+      <c r="I26" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G32" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H32" s="6">
+        <v>10.06</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K32" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G33" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H33" s="6">
+        <v>10.06</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K33" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G34" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H34" s="6">
+        <v>22.08</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K34" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G35" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H35" s="6">
+        <v>24.05</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K35" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J40" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J41" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="1">
+        <v>10282192302</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J42" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BAF9DE-2657-4950-949E-31649B1661DA}">
+  <dimension ref="A1:Q50"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="22.7109375" style="1" customWidth="1"/>
+    <col min="5" max="7" width="24.7109375" style="1" customWidth="1"/>
+    <col min="8" max="10" width="22.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.42578125" style="1" customWidth="1"/>
+    <col min="12" max="16" width="22.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="25" style="1" customWidth="1"/>
+    <col min="18" max="43" width="22.7109375" style="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="10"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+    </row>
+    <row r="15" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+    </row>
+    <row r="16" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+    </row>
+    <row r="17" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+    </row>
+    <row r="18" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+    </row>
+    <row r="19" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+    </row>
+    <row r="20" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="K22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N22" s="1">
+        <v>200</v>
+      </c>
+      <c r="O22" s="4"/>
+    </row>
+    <row r="23" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="K23" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N23" s="1">
+        <v>200</v>
+      </c>
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="K24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N24" s="1">
+        <v>180</v>
+      </c>
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+    </row>
+    <row r="33" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="K33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+    </row>
+    <row r="34" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="K34" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M34" s="6"/>
+    </row>
+    <row r="35" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K35" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="M35" s="6"/>
+    </row>
+    <row r="36" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="K36" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="K37" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+    </row>
+    <row r="39" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="1">
+        <v>3</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="1">
+        <v>4</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A968CA0-2687-4F0B-9EB0-3BCB4F5CAE17}">
+  <dimension ref="A1:Q220"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="22.7109375" style="1" customWidth="1"/>
+    <col min="5" max="7" width="24.7109375" style="1" customWidth="1"/>
+    <col min="8" max="10" width="22.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.42578125" style="1" customWidth="1"/>
+    <col min="12" max="16" width="22.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="25" style="1" customWidth="1"/>
+    <col min="18" max="43" width="22.7109375" style="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="10"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="10"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+    </row>
+    <row r="15" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+    </row>
+    <row r="16" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+    </row>
+    <row r="17" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+    </row>
+    <row r="18" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+    </row>
+    <row r="19" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+    </row>
+    <row r="20" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="K22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N22" s="1">
+        <v>200</v>
+      </c>
+      <c r="O22" s="4"/>
+    </row>
+    <row r="23" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="K23" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N23" s="1">
+        <v>200</v>
+      </c>
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="K24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N24" s="1">
+        <v>180</v>
+      </c>
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="26" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="5"/>
+    </row>
+    <row r="32" spans="2:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+    </row>
+    <row r="33" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="K33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+    </row>
+    <row r="34" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="K34" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="M34" s="6"/>
+    </row>
+    <row r="35" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K35" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="M35" s="6"/>
+    </row>
+    <row r="36" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="17" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E49" s="24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G53" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H55" s="22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C69" s="1">
+        <v>22.08</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C71" s="1">
+        <v>12.12</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C75" s="1">
+        <v>20</v>
+      </c>
+      <c r="D75" s="1">
+        <v>552</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C76" s="1">
+        <v>40</v>
+      </c>
+      <c r="D76" s="1">
+        <v>2632</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="17" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="17" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="1">
+        <v>22.08</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C87" s="1">
+        <v>12.12</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B96" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D97" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D98" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C99" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D99" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C100" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D100" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C101" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D101" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C102" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D102" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33FF386C-4E85-4194-9348-4CECDAC92CFA}">
+  <dimension ref="A1:X221"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="22.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.28515625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="41.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" style="1" customWidth="1"/>
+    <col min="12" max="15" width="32" style="1" customWidth="1"/>
+    <col min="16" max="16" width="29.85546875" style="1" customWidth="1"/>
+    <col min="17" max="23" width="22.7109375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25" style="1" customWidth="1"/>
+    <col min="25" max="50" width="22.7109375" style="1" customWidth="1"/>
+    <col min="51" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G1" s="55"/>
+      <c r="H1" s="51"/>
+    </row>
+    <row r="2" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="48" t="s">
+        <v>237</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="J2" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G3" s="56"/>
+      <c r="H3" s="57"/>
+      <c r="U3" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U5" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="V5" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>238</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>249</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="M6" s="50" t="s">
+        <v>283</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="O6" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="P6" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="S6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="T6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="U6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="V6" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="W6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="X6" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>223</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="K7" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="M7" s="50" t="s">
+        <v>284</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="O7" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="V7" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="X7" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="49" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="49" t="s">
+        <v>281</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="49" t="s">
+        <v>295</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="X8" s="11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="49" t="s">
+        <v>297</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="10"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="49" t="s">
+        <v>298</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="49" t="s">
+        <v>299</v>
+      </c>
+      <c r="K11" s="10"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="16"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="16"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R13" s="10"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+    </row>
+    <row r="15" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+    </row>
+    <row r="16" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="14"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+    </row>
+    <row r="17" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+    </row>
+    <row r="18" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+    </row>
+    <row r="19" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+    </row>
+    <row r="20" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="26"/>
+      <c r="S21" s="26"/>
+      <c r="T21" s="26"/>
+      <c r="U21" s="26"/>
+      <c r="V21" s="26"/>
+      <c r="W21" s="26"/>
+    </row>
+    <row r="22" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="26"/>
+      <c r="U22" s="26"/>
+      <c r="V22" s="27"/>
+      <c r="W22" s="26"/>
+    </row>
+    <row r="23" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="26"/>
+      <c r="T23" s="26"/>
+      <c r="U23" s="26"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="26"/>
+    </row>
+    <row r="24" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
+      <c r="S24" s="26"/>
+      <c r="T24" s="26"/>
+      <c r="U24" s="26"/>
+      <c r="V24" s="27"/>
+      <c r="W24" s="26"/>
+    </row>
+    <row r="25" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="26"/>
+      <c r="T25" s="26"/>
+      <c r="U25" s="26"/>
+      <c r="V25" s="27"/>
+      <c r="W25" s="26"/>
+    </row>
+    <row r="26" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="44"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="K26" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="26"/>
+      <c r="S26" s="26"/>
+      <c r="T26" s="26"/>
+      <c r="U26" s="26"/>
+      <c r="V26" s="26"/>
+      <c r="W26" s="26"/>
+    </row>
+    <row r="27" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>223</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>220</v>
+      </c>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="I27" s="53"/>
+      <c r="K27" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="L27" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="26"/>
+      <c r="T27" s="26"/>
+      <c r="U27" s="26"/>
+      <c r="V27" s="26"/>
+      <c r="W27" s="26"/>
+    </row>
+    <row r="28" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="4">
+        <v>1</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="38">
+        <v>0</v>
+      </c>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="I28" s="38"/>
+      <c r="K28" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="L28" s="27">
+        <v>1</v>
+      </c>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="26"/>
+      <c r="W28" s="26"/>
+    </row>
+    <row r="29" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="4">
+        <v>2</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="38">
+        <v>0</v>
+      </c>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+      <c r="K29" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="L29" s="27">
+        <v>1</v>
+      </c>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="26"/>
+      <c r="S29" s="26"/>
+      <c r="T29" s="26"/>
+      <c r="U29" s="26"/>
+      <c r="V29" s="26"/>
+      <c r="W29" s="26"/>
+    </row>
+    <row r="30" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="4">
+        <v>3</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="38">
+        <v>0</v>
+      </c>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="K30" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="L30" s="27">
+        <v>7</v>
+      </c>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="26"/>
+      <c r="T30" s="26"/>
+      <c r="U30" s="26"/>
+      <c r="V30" s="26"/>
+      <c r="W30" s="26"/>
+    </row>
+    <row r="31" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="4">
+        <v>4</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="D31" s="38">
+        <v>0</v>
+      </c>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="26"/>
+      <c r="S31" s="26"/>
+      <c r="T31" s="26"/>
+      <c r="U31" s="26"/>
+      <c r="V31" s="26"/>
+      <c r="W31" s="26"/>
+    </row>
+    <row r="32" spans="2:24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="4">
+        <v>5</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D32" s="38">
+        <v>0</v>
+      </c>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="26"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="26"/>
+    </row>
+    <row r="33" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="4">
+        <v>6</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" s="38">
+        <v>1</v>
+      </c>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="I33" s="38"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="26"/>
+      <c r="V33" s="26"/>
+      <c r="W33" s="26"/>
+    </row>
+    <row r="34" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="4">
+        <v>7</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="38">
+        <v>1</v>
+      </c>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="26"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="26"/>
+      <c r="V34" s="26"/>
+      <c r="W34" s="26"/>
+    </row>
+    <row r="35" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="4">
+        <v>8</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="38">
+        <v>1</v>
+      </c>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="26"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="26"/>
+      <c r="S35" s="26"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="26"/>
+      <c r="V35" s="26"/>
+      <c r="W35" s="26"/>
+    </row>
+    <row r="36" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="4">
+        <v>9</v>
+      </c>
+      <c r="C36" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="D36" s="38">
+        <v>1</v>
+      </c>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="26"/>
+      <c r="S36" s="26"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="26"/>
+      <c r="V36" s="26"/>
+      <c r="W36" s="26"/>
+    </row>
+    <row r="37" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="4">
+        <v>10</v>
+      </c>
+      <c r="C37" s="38" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" s="38">
+        <v>1</v>
+      </c>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="38"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="26"/>
+      <c r="S37" s="26"/>
+      <c r="T37" s="26"/>
+      <c r="U37" s="26"/>
+      <c r="V37" s="26"/>
+      <c r="W37" s="26"/>
+    </row>
+    <row r="38" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" s="27"/>
+      <c r="C38" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="D38" s="41">
+        <v>1</v>
+      </c>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="26"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="26"/>
+      <c r="S38" s="26"/>
+      <c r="T38" s="26"/>
+      <c r="U38" s="26"/>
+      <c r="V38" s="26"/>
+      <c r="W38" s="26"/>
+    </row>
+    <row r="39" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="27"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="26"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="26"/>
+      <c r="S39" s="26"/>
+      <c r="T39" s="26"/>
+      <c r="U39" s="26"/>
+      <c r="V39" s="26"/>
+      <c r="W39" s="26"/>
+    </row>
+    <row r="40" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
+      <c r="P40" s="26"/>
+      <c r="Q40" s="26"/>
+      <c r="R40" s="26"/>
+      <c r="S40" s="26"/>
+      <c r="T40" s="26"/>
+      <c r="U40" s="26"/>
+      <c r="V40" s="26"/>
+      <c r="W40" s="26"/>
+    </row>
+    <row r="41" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C41" s="51"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="26"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="26"/>
+      <c r="S41" s="26"/>
+      <c r="T41" s="26"/>
+      <c r="U41" s="26"/>
+      <c r="V41" s="26"/>
+      <c r="W41" s="26"/>
+    </row>
+    <row r="42" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="26"/>
+      <c r="S42" s="26"/>
+      <c r="T42" s="26"/>
+      <c r="U42" s="26"/>
+      <c r="V42" s="26"/>
+      <c r="W42" s="26"/>
+    </row>
+    <row r="43" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="39" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" s="46" t="s">
+        <v>267</v>
+      </c>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="26"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="26"/>
+      <c r="S43" s="26"/>
+      <c r="T43" s="26"/>
+      <c r="U43" s="26"/>
+      <c r="V43" s="26"/>
+      <c r="W43" s="26"/>
+    </row>
+    <row r="44" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="C44" s="27">
+        <v>1</v>
+      </c>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="26"/>
+      <c r="O44" s="26"/>
+      <c r="P44" s="26"/>
+      <c r="Q44" s="26"/>
+      <c r="R44" s="26"/>
+      <c r="S44" s="26"/>
+      <c r="T44" s="26"/>
+      <c r="U44" s="26"/>
+      <c r="V44" s="26"/>
+      <c r="W44" s="26"/>
+    </row>
+    <row r="45" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="C45" s="27">
+        <v>1</v>
+      </c>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="26"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="26"/>
+      <c r="O45" s="26"/>
+      <c r="P45" s="26"/>
+      <c r="Q45" s="26"/>
+      <c r="R45" s="26"/>
+      <c r="S45" s="26"/>
+      <c r="T45" s="26"/>
+      <c r="U45" s="26"/>
+      <c r="V45" s="26"/>
+      <c r="W45" s="26"/>
+    </row>
+    <row r="46" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="C46" s="27">
+        <v>1</v>
+      </c>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="26"/>
+      <c r="O46" s="26"/>
+      <c r="P46" s="26"/>
+      <c r="Q46" s="26"/>
+      <c r="R46" s="26"/>
+      <c r="S46" s="26"/>
+      <c r="T46" s="26"/>
+      <c r="U46" s="26"/>
+      <c r="V46" s="26"/>
+      <c r="W46" s="26"/>
+    </row>
+    <row r="47" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="52" t="s">
+        <v>272</v>
+      </c>
+      <c r="C47" s="27">
+        <v>2</v>
+      </c>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
+      <c r="K47" s="26"/>
+      <c r="L47" s="26"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="26"/>
+      <c r="O47" s="26"/>
+      <c r="P47" s="26"/>
+      <c r="Q47" s="26"/>
+      <c r="R47" s="26"/>
+      <c r="S47" s="26"/>
+      <c r="T47" s="26"/>
+      <c r="U47" s="26"/>
+      <c r="V47" s="26"/>
+      <c r="W47" s="26"/>
+    </row>
+    <row r="48" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="52" t="s">
+        <v>273</v>
+      </c>
+      <c r="C48" s="27">
+        <v>2</v>
+      </c>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="26"/>
+      <c r="K48" s="26"/>
+      <c r="L48" s="26"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="26"/>
+      <c r="Q48" s="26"/>
+      <c r="R48" s="26"/>
+      <c r="S48" s="26"/>
+      <c r="T48" s="26"/>
+      <c r="U48" s="26"/>
+      <c r="V48" s="26"/>
+      <c r="W48" s="26"/>
+    </row>
+    <row r="49" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="31"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="26"/>
+      <c r="K49" s="26"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="26"/>
+      <c r="O49" s="26"/>
+      <c r="P49" s="26"/>
+      <c r="Q49" s="26"/>
+      <c r="R49" s="26"/>
+      <c r="S49" s="26"/>
+      <c r="T49" s="26"/>
+      <c r="U49" s="26"/>
+      <c r="V49" s="26"/>
+      <c r="W49" s="26"/>
+    </row>
+    <row r="50" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="32"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="26"/>
+      <c r="L50" s="26"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="26"/>
+      <c r="O50" s="26"/>
+      <c r="P50" s="26"/>
+      <c r="Q50" s="26"/>
+      <c r="R50" s="26"/>
+      <c r="S50" s="26"/>
+      <c r="T50" s="26"/>
+      <c r="U50" s="26"/>
+      <c r="V50" s="26"/>
+      <c r="W50" s="26"/>
+    </row>
+    <row r="51" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="26"/>
+      <c r="K51" s="26"/>
+      <c r="L51" s="27"/>
+      <c r="M51" s="27"/>
+      <c r="N51" s="27"/>
+      <c r="O51" s="27"/>
+      <c r="P51" s="26"/>
+      <c r="Q51" s="26"/>
+      <c r="R51" s="26"/>
+      <c r="S51" s="26"/>
+      <c r="T51" s="26"/>
+      <c r="U51" s="26"/>
+      <c r="V51" s="26"/>
+      <c r="W51" s="26"/>
+    </row>
+    <row r="52" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="26"/>
+      <c r="K52" s="26"/>
+      <c r="L52" s="27"/>
+      <c r="M52" s="27"/>
+      <c r="N52" s="27"/>
+      <c r="O52" s="27"/>
+      <c r="P52" s="26"/>
+      <c r="Q52" s="26"/>
+      <c r="R52" s="26"/>
+      <c r="S52" s="26"/>
+      <c r="T52" s="26"/>
+      <c r="U52" s="26"/>
+      <c r="V52" s="26"/>
+      <c r="W52" s="26"/>
+    </row>
+    <row r="53" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="26"/>
+      <c r="K53" s="26"/>
+      <c r="L53" s="26"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="26"/>
+      <c r="O53" s="26"/>
+      <c r="P53" s="26"/>
+      <c r="Q53" s="26"/>
+      <c r="R53" s="26"/>
+      <c r="S53" s="26"/>
+      <c r="T53" s="26"/>
+      <c r="U53" s="26"/>
+      <c r="V53" s="26"/>
+      <c r="W53" s="26"/>
+    </row>
+    <row r="54" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="26"/>
+      <c r="J54" s="26"/>
+      <c r="K54" s="26"/>
+      <c r="L54" s="31"/>
+      <c r="M54" s="31"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="31"/>
+      <c r="P54" s="26"/>
+      <c r="Q54" s="26"/>
+      <c r="R54" s="26"/>
+      <c r="S54" s="26"/>
+      <c r="T54" s="26"/>
+      <c r="U54" s="26"/>
+      <c r="V54" s="26"/>
+      <c r="W54" s="26"/>
+    </row>
+    <row r="55" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="31"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="26"/>
+      <c r="J55" s="26"/>
+      <c r="K55" s="26"/>
+      <c r="L55" s="26"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="26"/>
+      <c r="O55" s="26"/>
+      <c r="P55" s="26"/>
+      <c r="Q55" s="26"/>
+      <c r="R55" s="26"/>
+      <c r="S55" s="26"/>
+      <c r="T55" s="26"/>
+      <c r="U55" s="26"/>
+      <c r="V55" s="26"/>
+      <c r="W55" s="26"/>
+    </row>
+    <row r="56" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="32"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="26"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="32"/>
+      <c r="M56" s="32"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="32"/>
+      <c r="P56" s="34"/>
+      <c r="Q56" s="26"/>
+      <c r="R56" s="26"/>
+      <c r="S56" s="26"/>
+      <c r="T56" s="26"/>
+      <c r="U56" s="26"/>
+      <c r="V56" s="26"/>
+      <c r="W56" s="26"/>
+    </row>
+    <row r="57" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="26"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="26"/>
+      <c r="O57" s="26"/>
+      <c r="P57" s="26"/>
+      <c r="Q57" s="26"/>
+      <c r="R57" s="26"/>
+      <c r="S57" s="26"/>
+      <c r="T57" s="26"/>
+      <c r="U57" s="26"/>
+      <c r="V57" s="26"/>
+      <c r="W57" s="26"/>
+    </row>
+    <row r="58" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="26"/>
+      <c r="L58" s="26"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="26"/>
+      <c r="O58" s="26"/>
+      <c r="P58" s="26"/>
+      <c r="Q58" s="26"/>
+      <c r="R58" s="26"/>
+      <c r="S58" s="26"/>
+      <c r="T58" s="26"/>
+      <c r="U58" s="26"/>
+      <c r="V58" s="26"/>
+      <c r="W58" s="26"/>
+    </row>
+    <row r="59" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26"/>
+      <c r="J59" s="26"/>
+      <c r="K59" s="26"/>
+      <c r="L59" s="26"/>
+      <c r="M59" s="26"/>
+      <c r="N59" s="26"/>
+      <c r="O59" s="26"/>
+      <c r="P59" s="26"/>
+      <c r="Q59" s="26"/>
+      <c r="R59" s="26"/>
+      <c r="S59" s="26"/>
+      <c r="T59" s="26"/>
+      <c r="U59" s="26"/>
+      <c r="V59" s="26"/>
+      <c r="W59" s="26"/>
+    </row>
+    <row r="60" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="26"/>
+      <c r="L60" s="26"/>
+      <c r="M60" s="26"/>
+      <c r="N60" s="26"/>
+      <c r="O60" s="26"/>
+      <c r="P60" s="26"/>
+      <c r="Q60" s="26"/>
+      <c r="R60" s="26"/>
+      <c r="S60" s="26"/>
+      <c r="T60" s="26"/>
+      <c r="U60" s="26"/>
+      <c r="V60" s="26"/>
+      <c r="W60" s="26"/>
+    </row>
+    <row r="61" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
+      <c r="R61" s="26"/>
+      <c r="S61" s="26"/>
+      <c r="T61" s="26"/>
+      <c r="U61" s="26"/>
+      <c r="V61" s="26"/>
+      <c r="W61" s="26"/>
+    </row>
+    <row r="62" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="27"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="26"/>
+      <c r="J62" s="26"/>
+      <c r="K62" s="26"/>
+      <c r="L62" s="26"/>
+      <c r="M62" s="26"/>
+      <c r="N62" s="26"/>
+      <c r="O62" s="26"/>
+      <c r="P62" s="26"/>
+      <c r="Q62" s="26"/>
+      <c r="R62" s="26"/>
+      <c r="S62" s="26"/>
+      <c r="T62" s="26"/>
+      <c r="U62" s="26"/>
+      <c r="V62" s="26"/>
+      <c r="W62" s="26"/>
+    </row>
+    <row r="63" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="27"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26"/>
+      <c r="K63" s="26"/>
+      <c r="L63" s="26"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="26"/>
+      <c r="O63" s="26"/>
+      <c r="P63" s="26"/>
+      <c r="Q63" s="26"/>
+      <c r="R63" s="26"/>
+      <c r="S63" s="26"/>
+      <c r="T63" s="26"/>
+      <c r="U63" s="26"/>
+      <c r="V63" s="26"/>
+      <c r="W63" s="26"/>
+    </row>
+    <row r="64" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="26"/>
+      <c r="K64" s="26"/>
+      <c r="L64" s="26"/>
+      <c r="M64" s="26"/>
+      <c r="N64" s="26"/>
+      <c r="O64" s="26"/>
+      <c r="P64" s="26"/>
+      <c r="Q64" s="26"/>
+      <c r="R64" s="26"/>
+      <c r="S64" s="26"/>
+      <c r="T64" s="26"/>
+      <c r="U64" s="26"/>
+      <c r="V64" s="26"/>
+      <c r="W64" s="26"/>
+    </row>
+    <row r="65" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="27"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="26"/>
+      <c r="K65" s="26"/>
+      <c r="L65" s="26"/>
+      <c r="M65" s="26"/>
+      <c r="N65" s="26"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="26"/>
+      <c r="Q65" s="26"/>
+      <c r="R65" s="26"/>
+      <c r="S65" s="26"/>
+      <c r="T65" s="26"/>
+      <c r="U65" s="26"/>
+      <c r="V65" s="26"/>
+      <c r="W65" s="26"/>
+    </row>
+    <row r="66" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="27"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="26"/>
+      <c r="K66" s="26"/>
+      <c r="L66" s="27"/>
+      <c r="M66" s="27"/>
+      <c r="N66" s="27"/>
+      <c r="O66" s="27"/>
+      <c r="P66" s="26"/>
+      <c r="Q66" s="26"/>
+      <c r="R66" s="26"/>
+      <c r="S66" s="26"/>
+      <c r="T66" s="26"/>
+      <c r="U66" s="26"/>
+      <c r="V66" s="26"/>
+      <c r="W66" s="26"/>
+    </row>
+    <row r="67" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="26"/>
+      <c r="J67" s="26"/>
+      <c r="K67" s="26"/>
+      <c r="L67" s="26"/>
+      <c r="M67" s="26"/>
+      <c r="N67" s="26"/>
+      <c r="O67" s="26"/>
+      <c r="P67" s="26"/>
+      <c r="Q67" s="26"/>
+      <c r="R67" s="26"/>
+      <c r="S67" s="26"/>
+      <c r="T67" s="26"/>
+      <c r="U67" s="26"/>
+      <c r="V67" s="26"/>
+      <c r="W67" s="26"/>
+    </row>
+    <row r="68" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="31"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="26"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="26"/>
+      <c r="J68" s="26"/>
+      <c r="K68" s="26"/>
+      <c r="L68" s="31"/>
+      <c r="M68" s="31"/>
+      <c r="N68" s="31"/>
+      <c r="O68" s="31"/>
+      <c r="P68" s="26"/>
+      <c r="Q68" s="26"/>
+      <c r="R68" s="26"/>
+      <c r="S68" s="26"/>
+      <c r="T68" s="26"/>
+      <c r="U68" s="26"/>
+      <c r="V68" s="26"/>
+      <c r="W68" s="26"/>
+    </row>
+    <row r="69" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="32"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="35"/>
+      <c r="I69" s="35"/>
+      <c r="J69" s="26"/>
+      <c r="K69" s="26"/>
+      <c r="L69" s="28"/>
+      <c r="M69" s="28"/>
+      <c r="N69" s="28"/>
+      <c r="O69" s="28"/>
+      <c r="P69" s="28"/>
+      <c r="Q69" s="26"/>
+      <c r="R69" s="26"/>
+      <c r="S69" s="26"/>
+      <c r="T69" s="26"/>
+      <c r="U69" s="26"/>
+      <c r="V69" s="26"/>
+      <c r="W69" s="26"/>
+    </row>
+    <row r="70" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+      <c r="J70" s="26"/>
+      <c r="K70" s="26"/>
+      <c r="L70" s="35"/>
+      <c r="M70" s="35"/>
+      <c r="N70" s="35"/>
+      <c r="O70" s="35"/>
+      <c r="P70" s="35"/>
+      <c r="Q70" s="26"/>
+      <c r="R70" s="26"/>
+      <c r="S70" s="26"/>
+      <c r="T70" s="26"/>
+      <c r="U70" s="26"/>
+      <c r="V70" s="26"/>
+      <c r="W70" s="26"/>
+    </row>
+    <row r="71" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="26"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="26"/>
+      <c r="J71" s="26"/>
+      <c r="K71" s="26"/>
+      <c r="L71" s="26"/>
+      <c r="M71" s="26"/>
+      <c r="N71" s="26"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="26"/>
+      <c r="Q71" s="26"/>
+      <c r="R71" s="26"/>
+      <c r="S71" s="26"/>
+      <c r="T71" s="26"/>
+      <c r="U71" s="26"/>
+      <c r="V71" s="26"/>
+      <c r="W71" s="26"/>
+    </row>
+    <row r="72" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+      <c r="K72" s="26"/>
+      <c r="L72" s="26"/>
+      <c r="M72" s="26"/>
+      <c r="N72" s="26"/>
+      <c r="O72" s="26"/>
+      <c r="P72" s="26"/>
+      <c r="Q72" s="26"/>
+      <c r="R72" s="26"/>
+      <c r="S72" s="26"/>
+      <c r="T72" s="26"/>
+      <c r="U72" s="26"/>
+      <c r="V72" s="26"/>
+      <c r="W72" s="26"/>
+    </row>
+    <row r="73" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
+      <c r="N73" s="26"/>
+      <c r="O73" s="26"/>
+      <c r="P73" s="26"/>
+      <c r="Q73" s="26"/>
+      <c r="R73" s="26"/>
+      <c r="S73" s="26"/>
+      <c r="T73" s="26"/>
+      <c r="U73" s="26"/>
+      <c r="V73" s="26"/>
+      <c r="W73" s="26"/>
+    </row>
+    <row r="74" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="31"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+      <c r="J74" s="28"/>
+      <c r="K74" s="26"/>
+      <c r="L74" s="26"/>
+      <c r="M74" s="26"/>
+      <c r="N74" s="26"/>
+      <c r="O74" s="26"/>
+      <c r="P74" s="26"/>
+      <c r="Q74" s="26"/>
+      <c r="R74" s="26"/>
+      <c r="S74" s="26"/>
+      <c r="T74" s="26"/>
+      <c r="U74" s="26"/>
+      <c r="V74" s="26"/>
+      <c r="W74" s="26"/>
+    </row>
+    <row r="75" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="32"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="37"/>
+      <c r="I75" s="37"/>
+      <c r="J75" s="35"/>
+      <c r="K75" s="26"/>
+      <c r="L75" s="26"/>
+      <c r="M75" s="26"/>
+      <c r="N75" s="26"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="26"/>
+      <c r="Q75" s="26"/>
+      <c r="R75" s="26"/>
+      <c r="S75" s="26"/>
+      <c r="T75" s="26"/>
+      <c r="U75" s="26"/>
+      <c r="V75" s="26"/>
+      <c r="W75" s="26"/>
+    </row>
+    <row r="76" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="26"/>
+      <c r="N76" s="26"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="26"/>
+      <c r="Q76" s="26"/>
+      <c r="R76" s="26"/>
+      <c r="S76" s="26"/>
+      <c r="T76" s="26"/>
+      <c r="U76" s="26"/>
+      <c r="V76" s="26"/>
+      <c r="W76" s="26"/>
+    </row>
+    <row r="77" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
+      <c r="I77" s="26"/>
+      <c r="J77" s="26"/>
+      <c r="K77" s="26"/>
+      <c r="L77" s="26"/>
+      <c r="M77" s="26"/>
+      <c r="N77" s="26"/>
+      <c r="O77" s="26"/>
+      <c r="P77" s="26"/>
+      <c r="Q77" s="26"/>
+      <c r="R77" s="26"/>
+      <c r="S77" s="26"/>
+      <c r="T77" s="26"/>
+      <c r="U77" s="26"/>
+      <c r="V77" s="26"/>
+      <c r="W77" s="26"/>
+    </row>
+    <row r="78" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="26"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="26"/>
+      <c r="N78" s="26"/>
+      <c r="O78" s="26"/>
+      <c r="P78" s="26"/>
+      <c r="Q78" s="26"/>
+      <c r="R78" s="26"/>
+      <c r="S78" s="26"/>
+      <c r="T78" s="26"/>
+      <c r="U78" s="26"/>
+      <c r="V78" s="26"/>
+      <c r="W78" s="26"/>
+    </row>
+    <row r="79" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="27"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="26"/>
+      <c r="J79" s="26"/>
+      <c r="K79" s="26"/>
+      <c r="L79" s="26"/>
+      <c r="M79" s="26"/>
+      <c r="N79" s="26"/>
+      <c r="O79" s="26"/>
+      <c r="P79" s="26"/>
+      <c r="Q79" s="26"/>
+      <c r="R79" s="26"/>
+      <c r="S79" s="26"/>
+      <c r="T79" s="26"/>
+      <c r="U79" s="26"/>
+      <c r="V79" s="26"/>
+      <c r="W79" s="26"/>
+    </row>
+    <row r="80" spans="2:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="4"/>
+    </row>
+    <row r="81" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="17"/>
+    </row>
+    <row r="82" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="17"/>
+    </row>
+    <row r="83" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="11"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="10"/>
+      <c r="I85" s="54"/>
+    </row>
+    <row r="86" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
+      <c r="G87" s="7"/>
+    </row>
+    <row r="88" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="3"/>
+    </row>
+    <row r="91" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="11"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="55"/>
+    </row>
+    <row r="92" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="3"/>
+    </row>
+    <row r="97" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B97" s="22"/>
+      <c r="C97" s="22"/>
+      <c r="D97" s="22"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="22"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="55"/>
+    </row>
+    <row r="98" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="19"/>
+      <c r="C98" s="19"/>
+      <c r="D98" s="19"/>
+      <c r="E98" s="19"/>
+      <c r="F98" s="19"/>
+      <c r="G98" s="19"/>
+    </row>
+    <row r="99" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="19"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="19"/>
+      <c r="E99" s="19"/>
+      <c r="F99" s="19"/>
+      <c r="G99" s="19"/>
+    </row>
+    <row r="100" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="20"/>
+      <c r="C100" s="20"/>
+      <c r="D100" s="20"/>
+      <c r="E100" s="20"/>
+      <c r="F100" s="20"/>
+      <c r="G100" s="20"/>
+    </row>
+    <row r="101" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="20"/>
+      <c r="C101" s="20"/>
+      <c r="D101" s="20"/>
+      <c r="E101" s="20"/>
+      <c r="F101" s="20"/>
+      <c r="G101" s="20"/>
+    </row>
+    <row r="102" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="20"/>
+      <c r="C102" s="20"/>
+      <c r="D102" s="20"/>
+      <c r="E102" s="20"/>
+      <c r="F102" s="20"/>
+      <c r="G102" s="20"/>
+    </row>
+    <row r="103" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="21"/>
+      <c r="C103" s="21"/>
+      <c r="D103" s="21"/>
+      <c r="E103" s="21"/>
+      <c r="F103" s="21"/>
+      <c r="G103" s="21"/>
+    </row>
+    <row r="104" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="24" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C26:D26"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B44" r:id="rId1" xr:uid="{A12A56EA-DD77-4B21-B871-280B426AB998}"/>
+    <hyperlink ref="B45" r:id="rId2" xr:uid="{DD7C436D-41E7-4B88-8FE4-C01371E67673}"/>
+    <hyperlink ref="B46" r:id="rId3" xr:uid="{623163C2-ADE6-4237-BE63-CD3468F56975}"/>
+    <hyperlink ref="B47" r:id="rId4" xr:uid="{2177B22D-D58C-44B4-9E03-04463B2F31A7}"/>
+    <hyperlink ref="B48" r:id="rId5" xr:uid="{03FBBD7B-915A-49B1-BE50-253850FA5EA1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>